--- a/products_template.xlsx
+++ b/products_template.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laptopshop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN\CHD\sunny-shop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47267C25-E8F8-49F1-9BA0-5B5AC85758E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55340E26-FC56-444C-BAD7-EF443958AB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Factory</t>
+    <t>Brand</t>
   </si>
   <si>
     <t>Target</t>
@@ -46,89 +46,31 @@
     <t>Category</t>
   </si>
   <si>
-    <t>https://abramillar.com/wp-content/uploads/2018/01/apple-1842297_1920.jpg</t>
-  </si>
-  <si>
-    <t>Short description</t>
-  </si>
-  <si>
-    <t>Dell</t>
-  </si>
-  <si>
-    <t>Gaming</t>
-  </si>
-  <si>
-    <t>Macbook</t>
-  </si>
-  <si>
-    <t>Macbook Air M1</t>
-  </si>
-  <si>
-    <t>Macbook Air M2</t>
-  </si>
-  <si>
-    <t>Macbook Air M3</t>
-  </si>
-  <si>
-    <t>Macbook Air M4</t>
-  </si>
-  <si>
-    <t>Macbook Air M5</t>
-  </si>
-  <si>
-    <t>Macbook Air M6</t>
-  </si>
-  <si>
-    <t>Macbook Air M7</t>
-  </si>
-  <si>
-    <t>Macbook Air M8</t>
-  </si>
-  <si>
-    <t>Macbook Air M9</t>
-  </si>
-  <si>
-    <t>Macbook Air M10</t>
-  </si>
-  <si>
-    <t>Macbook Air M11</t>
-  </si>
-  <si>
-    <t>Macbook Air M12</t>
-  </si>
-  <si>
-    <t>Macbook Air M13</t>
-  </si>
-  <si>
-    <t>Macbook Air M14</t>
-  </si>
-  <si>
-    <t>Macbook Air M15</t>
+    <t>https://down-vn.img.susercontent.com/file/vn-11134207-7qukw-lju0wkebupz659_tn</t>
+  </si>
+  <si>
+    <t>Quần Short unisex chất cotton cao cấp,Quần Short nam nữ phong cách thể thao -NANA SHOP.</t>
+  </si>
+  <si>
+    <t>Nike</t>
+  </si>
+  <si>
+    <t>Unisex</t>
+  </si>
+  <si>
+    <t>Quần</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -149,241 +91,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -396,7 +114,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -412,7 +130,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -424,7 +142,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -438,12 +156,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -471,14 +189,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -506,6 +241,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -648,23 +400,30 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -690,21 +449,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>50000</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>100000</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -716,21 +475,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>1001</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>50001</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -742,21 +501,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>1002</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>50002</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>100002</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -768,21 +527,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>1003</v>
-      </c>
-      <c r="C5" s="1" t="s">
+        <v>50003</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>100003</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -794,21 +553,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>1004</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>50004</v>
+      </c>
+      <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>100004</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -820,21 +579,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>1005</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>50005</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>100005</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -846,21 +605,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>1006</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>50006</v>
+      </c>
+      <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>100006</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -872,21 +631,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>1007</v>
-      </c>
-      <c r="C9" s="1" t="s">
+        <v>50007</v>
+      </c>
+      <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>100007</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -898,21 +657,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>1008</v>
-      </c>
-      <c r="C10" s="1" t="s">
+        <v>50008</v>
+      </c>
+      <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>100008</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -924,21 +683,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>1009</v>
-      </c>
-      <c r="C11" s="1" t="s">
+        <v>50009</v>
+      </c>
+      <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>100009</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -950,21 +709,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B12">
-        <v>1010</v>
-      </c>
-      <c r="C12" s="1" t="s">
+        <v>50010</v>
+      </c>
+      <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>100010</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -976,129 +735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13">
-        <v>1011</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>1012</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14">
-        <v>22</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>1013</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>1014</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{D5F83608-C7C4-416A-8C6F-ED38CFB4C3E3}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{35E577DB-AEB4-44FE-B184-0EF0060710FF}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{C4252D28-6EC8-4645-A96B-53E3888D3DCD}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{484261B8-2A3A-408D-928F-6B624BE115DE}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{C9FABA6C-50BC-4F72-99E1-36BD7DD58A5C}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{BF1FEEF5-62B5-4F77-AA4E-7108F50663C5}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{819E6BBF-9ED1-47A2-BA49-2FEE2E5B7F00}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{9B6C629C-BD0F-46E1-BFE6-0EAD7AD4BA3A}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{D10E1056-254B-409A-8F2F-2AF6F04804C4}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{CA1C98AD-F2FB-437A-91FA-6243D593AAE3}"/>
-    <hyperlink ref="C13" r:id="rId12" xr:uid="{B4207EFC-C083-4CA7-8F4F-838DA98A0F9C}"/>
-    <hyperlink ref="C14" r:id="rId13" xr:uid="{C1C79010-9AA6-4A2C-8F51-C96E558051FB}"/>
-    <hyperlink ref="C15" r:id="rId14" xr:uid="{0F16DFF6-6822-4E50-B837-89F4FCC89759}"/>
-    <hyperlink ref="C16" r:id="rId15" xr:uid="{C71C2E4E-47AA-49CE-9FB0-966B18560EFF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>